--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -268,7 +268,7 @@
     <t>Mind</t>
   </si>
   <si>
-    <t>life/-15,mana/60,SPD/25,EDR/20,PDR/10,resNether/5,resChaos/5,resMagic/20,innocence/-20,featManaMeat/2,featFastFucker/2,mc_aun_featDemonBlood/1,mc_aun_featManaAbsorber/1</t>
+    <t>life/-15,mana/60,SPD/25,EDR/20,PDR/10,resNether/5,resChaos/5,resMagic/20,innocence/-20,featManaMeat/2,featFastFucker/2,mc_aun_featDemonBlood/1,mc_aun_featManaAbsorber/2</t>
   </si>
   <si>
     <t>f/21/150/43/rude|わたし|お前/default</t>
@@ -522,10 +522,10 @@
     <t>種族により受け継がれた特性。</t>
   </si>
   <si>
-    <t>あなたは気持ちいいことを通じてマナを吸う。</t>
-  </si>
-  <si>
-    <t>イタズラに成功すると対象のマナを吸収する</t>
+    <t>あなたはマナを吸う。</t>
+  </si>
+  <si>
+    <t>魔法によるダメージの一部をマナとして吸収する,イタズラに成功すると対象のマナを奪う</t>
   </si>
   <si>
     <t>395820002</t>
@@ -3418,7 +3418,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>162</v>
       </c>
       <c r="AH4" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="AR4" t="s">
         <v>163</v>
@@ -6186,7 +6186,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>166</v>
       </c>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="204">
   <si>
     <t>id</t>
   </si>
@@ -278,6 +278,51 @@
   </si>
   <si>
     <t>Feel</t>
+  </si>
+  <si>
+    <t>mc_aun_eirwen</t>
+  </si>
+  <si>
+    <t>エイルウェン</t>
+  </si>
+  <si>
+    <t>Zaya</t>
+  </si>
+  <si>
+    <t>風と踊る</t>
+  </si>
+  <si>
+    <t>の</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>addZone(palmia),addDrama()</t>
+  </si>
+  <si>
+    <t>elea</t>
+  </si>
+  <si>
+    <t>mc_araj_monk</t>
+  </si>
+  <si>
+    <t>1,100</t>
+  </si>
+  <si>
+    <t>mc_aun_ActMultiMartialMelee/70</t>
+  </si>
+  <si>
+    <t>SPD/40,evasionPerfect/15,mod_flurry/30,mc_araj_featMonk/1</t>
+  </si>
+  <si>
+    <t>f/16/162/49/friendly|私|君/confident</t>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>Exercise</t>
   </si>
   <si>
     <t>calm_JP</t>
@@ -336,6 +381,25 @@
 ミザリーは尻尾を一振りした。</t>
   </si>
   <si>
+    <t>「どこかに強い奴はいないかなー」</t>
+  </si>
+  <si>
+    <t>「いくよ！」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「うそっ…！？」
+「…」</t>
+  </si>
+  <si>
+    <t>「きまり！」</t>
+  </si>
+  <si>
+    <t>「かなー」</t>
+  </si>
+  <si>
+    <t>「うそっ…！？」</t>
+  </si>
+  <si>
     <t>alias</t>
   </si>
   <si>
@@ -492,9 +556,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>395820001</t>
   </si>
   <si>
@@ -541,13 +602,52 @@
   </si>
   <si>
     <t>起きている相手をイタズラの対象にできる</t>
+  </si>
+  <si>
+    <t>mc_aun_ActMultiMartialMelee</t>
+  </si>
+  <si>
+    <t>拳足乱舞</t>
+  </si>
+  <si>
+    <t>Wild Dance</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>ActMCAUNMultiMartialMelee</t>
+  </si>
+  <si>
+    <t>ABILITY</t>
+  </si>
+  <si>
+    <t>ability</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>neg,CD_npc</t>
+  </si>
+  <si>
+    <t>対象に素早い連続攻撃を行う。</t>
+  </si>
+  <si>
+    <t>Shower the target with blows</t>
+  </si>
+  <si>
+    <t>暗器以外の武器を装備していると使用不可</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -561,6 +661,11 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -584,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -599,7 +704,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -3493,6 +3602,80 @@
       </c>
       <c r="AQ4" s="4" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4497,34 +4680,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4607,29 +4790,58 @@
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>99</v>
+      <c r="C4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>99</v>
+        <v>116</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5620,618 +5832,1728 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BE5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:BY1000"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="77" width="8.71" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N1" t="s">
-        <v>112</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" t="s">
-        <v>114</v>
-      </c>
-      <c r="S1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="Q1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W1" t="s">
-        <v>118</v>
-      </c>
-      <c r="X1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="U1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Z1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AR1" t="s">
+      <c r="AC1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AR1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AT1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>147</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="AT1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="AU1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="AV1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AW1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AX1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="AY1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="AZ1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="BA1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="BB1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="BC1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="BD1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="BE1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="4"/>
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
+      <c r="BT1" s="4"/>
+      <c r="BU1" s="4"/>
+      <c r="BV1" s="4"/>
+      <c r="BW1" s="4"/>
+      <c r="BX1" s="4"/>
+      <c r="BY1" s="4"/>
+    </row>
+    <row r="2" spans="1:77" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AG2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AG2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AP2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="AP2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AT2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AU2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AX2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AY2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AZ2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="BF2" s="4"/>
+      <c r="BG2" s="4"/>
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="4"/>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="4"/>
+      <c r="BN2" s="4"/>
+      <c r="BO2" s="4"/>
+      <c r="BP2" s="4"/>
+      <c r="BQ2" s="4"/>
+      <c r="BR2" s="4"/>
+      <c r="BS2" s="4"/>
+      <c r="BT2" s="4"/>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="4"/>
+      <c r="BW2" s="4"/>
+      <c r="BX2" s="4"/>
+      <c r="BY2" s="4"/>
+    </row>
+    <row r="3" spans="1:77" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="M3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="M3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="P3" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>59</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="P3" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="T3" t="s">
-        <v>59</v>
-      </c>
-      <c r="U3" t="s">
-        <v>59</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
-      </c>
-      <c r="W3" t="s">
-        <v>151</v>
-      </c>
-      <c r="X3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>59</v>
-      </c>
+      <c r="T3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AN3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AS3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AW3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AX3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AY3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AZ3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BB3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BC3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BE3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BF3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
+      <c r="BN3" s="4"/>
+      <c r="BO3" s="4"/>
+      <c r="BP3" s="4"/>
+      <c r="BQ3" s="4"/>
+      <c r="BR3" s="4"/>
+      <c r="BS3" s="4"/>
+      <c r="BT3" s="4"/>
+      <c r="BU3" s="4"/>
+      <c r="BV3" s="4"/>
+      <c r="BW3" s="4"/>
+      <c r="BX3" s="4"/>
+      <c r="BY3" s="4"/>
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="A4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="S4" t="s">
-        <v>158</v>
-      </c>
-      <c r="W4" t="s">
-        <v>159</v>
-      </c>
-      <c r="X4" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>163</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>164</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>165</v>
+      <c r="S4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AV4" s="4" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="S5" t="s">
-        <v>158</v>
-      </c>
-      <c r="W5" t="s">
-        <v>159</v>
-      </c>
-      <c r="X5" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH5" t="s">
+      <c r="S5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AR5" t="s">
-        <v>163</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>169</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>170</v>
-      </c>
-    </row>
+      <c r="AR5" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT5" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV5" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>395820003</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J6" s="7">
+        <v>5</v>
+      </c>
+      <c r="K6" s="8">
+        <v>100</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="O6" s="8"/>
+      <c r="R6" s="8">
+        <v>10</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>10</v>
+      </c>
+      <c r="AH6" s="4"/>
+      <c r="AR6" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="AS6" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT6" s="4"/>
+      <c r="AV6" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -244,7 +244,7 @@
     <t>Friend</t>
   </si>
   <si>
-    <t>addZone(tinkerCamp),addBio()</t>
+    <t>addZone(tinkerCamp),addBio(),addDrama()</t>
   </si>
   <si>
     <t>UniqueChara</t>
@@ -271,7 +271,7 @@
     <t>life/-15,mana/60,SPD/25,EDR/20,PDR/10,resNether/5,resChaos/5,resMagic/20,innocence/-20,featManaMeat/2,featFastFucker/2,mc_aun_featDemonBlood/1,mc_aun_featManaAbsorber/2</t>
   </si>
   <si>
-    <t>f/21/150/43/rude|わたし|お前/default</t>
+    <t>f/21/150/43/rude|わたし|お前/mc_aun_misalie</t>
   </si>
   <si>
     <t>Diary</t>
@@ -286,19 +286,19 @@
     <t>エイルウェン</t>
   </si>
   <si>
-    <t>Zaya</t>
+    <t>Eirwen</t>
   </si>
   <si>
     <t>風と踊る</t>
   </si>
   <si>
-    <t>の</t>
+    <t>Wind-Dancing</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>addZone(palmia),addDrama()</t>
+    <t>addZone(palmia),addDrama(),addBio()</t>
   </si>
   <si>
     <t>elea</t>
@@ -316,7 +316,7 @@
     <t>SPD/40,evasionPerfect/15,mod_flurry/30,mc_araj_featMonk/1</t>
   </si>
   <si>
-    <t>f/16/162/49/friendly|私|君/confident</t>
+    <t>f/16/162/49/friendly|私|君/mc_aun_eirwen</t>
   </si>
   <si>
     <t>Explore</t>
@@ -391,13 +391,16 @@
 「…」</t>
   </si>
   <si>
+    <t>「とどめ！」</t>
+  </si>
+  <si>
+    <t>「かなー」</t>
+  </si>
+  <si>
+    <t>「うそっ…！？」</t>
+  </si>
+  <si>
     <t>「きまり！」</t>
-  </si>
-  <si>
-    <t>「かなー」</t>
-  </si>
-  <si>
-    <t>「うそっ…！？」</t>
   </si>
   <si>
     <t>alias</t>
@@ -4841,7 +4844,7 @@
         <v>122</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5844,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>9</v>
@@ -5853,34 +5856,34 @@
         <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>22</v>
@@ -5889,85 +5892,85 @@
         <v>23</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>39</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AI1" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AK1" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL1" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM1" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN1" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO1" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AP1" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AQ1" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AR1" s="4" t="s">
         <v>53</v>
@@ -5976,40 +5979,40 @@
         <v>54</v>
       </c>
       <c r="AT1" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AU1" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AV1" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AW1" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AX1" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AY1" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AZ1" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BA1" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BB1" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BC1" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BD1" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BE1" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BF1" s="4"/>
       <c r="BG1" s="4"/>
@@ -6061,7 +6064,7 @@
         <v>55</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>56</v>
@@ -6130,7 +6133,7 @@
         <v>56</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AH2" s="4" t="s">
         <v>56</v>
@@ -6272,7 +6275,7 @@
         <v>63</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>59</v>
@@ -6293,7 +6296,7 @@
         <v>59</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>59</v>
@@ -6314,13 +6317,13 @@
         <v>59</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AE3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG3" s="4" t="s">
         <v>93</v>
@@ -6420,13 +6423,13 @@
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>61</v>
@@ -6435,42 +6438,42 @@
         <v>61</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AH4" s="4" t="s">
         <v>93</v>
       </c>
       <c r="AR4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AT4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AV4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>61</v>
@@ -6479,31 +6482,31 @@
         <v>61</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AH5" s="4" t="s">
         <v>63</v>
       </c>
       <c r="AR5" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AV5" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
@@ -6511,16 +6514,16 @@
         <v>395820003</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J6" s="7">
         <v>5</v>
@@ -6534,42 +6537,42 @@
         <v>10</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE6" s="8">
         <v>10</v>
       </c>
       <c r="AH6" s="4"/>
       <c r="AR6" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AS6" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AT6" s="4"/>
       <c r="AV6" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="213">
   <si>
     <t>id</t>
   </si>
@@ -637,10 +637,34 @@
     <t>neg,CD_npc</t>
   </si>
   <si>
-    <t>対象に素早い連続攻撃を行う。</t>
+    <t>対象に拳や蹴りなどで素早い連撃を行う。</t>
   </si>
   <si>
     <t>Shower the target with blows</t>
+  </si>
+  <si>
+    <t>暗器以外の武器を装備していると使用不可,武器の数によりスタミナ消費量が変動</t>
+  </si>
+  <si>
+    <t>395820004</t>
+  </si>
+  <si>
+    <t>mc_aun_ActMartialMeleeSwarm</t>
+  </si>
+  <si>
+    <t>大円蹴り</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>ActMCAUNMultiMartialSwarm</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>周囲の対象に回し蹴りを浴びせる。</t>
   </si>
   <si>
     <t>暗器以外の武器を装備していると使用不可</t>
@@ -3530,7 +3554,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -3607,7 +3631,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
@@ -5835,7 +5859,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BY1000"/>
+  <dimension ref="A1:BY999"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6421,7 +6445,7 @@
       <c r="BX3" s="4"/>
       <c r="BY3" s="4"/>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>176</v>
       </c>
@@ -6465,7 +6489,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>187</v>
       </c>
@@ -6509,7 +6533,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>395820003</v>
       </c>
@@ -6575,6 +6599,69 @@
         <v>204</v>
       </c>
     </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" t="s">
+        <v>195</v>
+      </c>
+      <c r="J7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" t="s">
+        <v>172</v>
+      </c>
+      <c r="R7" t="s">
+        <v>208</v>
+      </c>
+      <c r="S7" t="s">
+        <v>179</v>
+      </c>
+      <c r="U7" t="s">
+        <v>196</v>
+      </c>
+      <c r="W7" t="s">
+        <v>209</v>
+      </c>
+      <c r="X7" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7554,7 +7641,6 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="220">
   <si>
     <t>id</t>
   </si>
@@ -310,7 +310,7 @@
     <t>1,100</t>
   </si>
   <si>
-    <t>mc_aun_ActMultiMartialMelee/70</t>
+    <t>mc_aun_ActWindMartialSwarm/35,mc_aun_ActWindMartialMultiHit/50,mc_aun_ActWindMartialCounter/15</t>
   </si>
   <si>
     <t>SPD/40,evasionPerfect/15,mod_flurry/30,mc_araj_featMonk/1</t>
@@ -607,10 +607,10 @@
     <t>起きている相手をイタズラの対象にできる</t>
   </si>
   <si>
-    <t>mc_aun_ActMultiMartialMelee</t>
-  </si>
-  <si>
-    <t>拳足乱舞</t>
+    <t>mc_aun_ActWindMartialMultiHit</t>
+  </si>
+  <si>
+    <t>一陣乱舞</t>
   </si>
   <si>
     <t>Wild Dance</t>
@@ -622,7 +622,7 @@
     <t>Ground</t>
   </si>
   <si>
-    <t>ActMCAUNMultiMartialMelee</t>
+    <t>ActMCAUNMartialMultiHit</t>
   </si>
   <si>
     <t>ABILITY</t>
@@ -634,7 +634,7 @@
     <t>attack</t>
   </si>
   <si>
-    <t>neg,CD_npc</t>
+    <t>neg,CD_npc,recovery</t>
   </si>
   <si>
     <t>対象に拳や蹴りなどで素早い連撃を行う。</t>
@@ -649,25 +649,46 @@
     <t>395820004</t>
   </si>
   <si>
-    <t>mc_aun_ActMartialMeleeSwarm</t>
-  </si>
-  <si>
-    <t>大円蹴り</t>
+    <t>mc_aun_ActWindMartialSwarm</t>
+  </si>
+  <si>
+    <t>辻風払い</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>ActMCAUNMultiMartialSwarm</t>
+    <t>ActMCAUNMartialSwarm</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>周囲の対象に回し蹴りを浴びせる。</t>
+    <t>周囲の対象に拳や蹴りなどを浴びせる。</t>
   </si>
   <si>
     <t>暗器以外の武器を装備していると使用不可</t>
+  </si>
+  <si>
+    <t>395820005</t>
+  </si>
+  <si>
+    <t>mc_aun_ActWindMartialCounter</t>
+  </si>
+  <si>
+    <t>凪返し</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>ActMCAUNMartialCounter</t>
+  </si>
+  <si>
+    <t>次の行動まで構えを取り、攻撃してきた対象に強烈な反撃を行う。</t>
   </si>
 </sst>
 </file>
@@ -6661,6 +6682,68 @@
         <v>212</v>
       </c>
     </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" t="s">
+        <v>172</v>
+      </c>
+      <c r="R8" t="s">
+        <v>216</v>
+      </c>
+      <c r="S8" t="s">
+        <v>179</v>
+      </c>
+      <c r="U8" t="s">
+        <v>217</v>
+      </c>
+      <c r="W8" t="s">
+        <v>218</v>
+      </c>
+      <c r="X8" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>219</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>212</v>
+      </c>
+    </row>
     <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="Chara" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="CharaText" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Element" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Stat" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="259">
   <si>
     <t>id</t>
   </si>
@@ -268,7 +269,7 @@
     <t>Mind</t>
   </si>
   <si>
-    <t>life/-15,mana/60,SPD/25,EDR/20,PDR/10,resNether/5,resChaos/5,resMagic/20,innocence/-20,featManaMeat/2,featFastFucker/2,mc_aun_featDemonBlood/1,mc_aun_featManaAbsorber/2</t>
+    <t>life/-15,mana/60,SPD/25,EDR/20,PDR/10,resNether/5,resChaos/5,resMagic/20,innocence/-20,featManaMeat/2,featFastFucker/2,FeatMCAUNDemonBlood/1,FeatMCAUNManaAbsorber/2</t>
   </si>
   <si>
     <t>f/21/150/43/rude|わたし|お前/mc_aun_misalie</t>
@@ -310,10 +311,10 @@
     <t>1,100</t>
   </si>
   <si>
-    <t>mc_aun_ActWindMartialSwarm/35,mc_aun_ActWindMartialMultiHit/50,mc_aun_ActWindMartialCounter/15</t>
-  </si>
-  <si>
-    <t>SPD/40,evasionPerfect/15,mod_flurry/30,mc_araj_featMonk/1</t>
+    <t>ActMCAUNWindMartialSwarm/35,ActMCAUNWindMartialMultiHit/50,ActMCAUNWindMartialCounter/15</t>
+  </si>
+  <si>
+    <t>SPD/40,evasionPerfect/5,mod_flurry/30,mc_araj_featMonk/1</t>
   </si>
   <si>
     <t>f/16/162/49/friendly|私|君/mc_aun_eirwen</t>
@@ -562,7 +563,7 @@
     <t>395820001</t>
   </si>
   <si>
-    <t>mc_aun_featManaAbsorber</t>
+    <t>FeatMCAUNManaAbsorber</t>
   </si>
   <si>
     <t>マナ吸い体質</t>
@@ -595,7 +596,7 @@
     <t>395820002</t>
   </si>
   <si>
-    <t>mc_aun_featDemonBlood</t>
+    <t>FeatMCAUNDemonBlood</t>
   </si>
   <si>
     <t>悪魔の血</t>
@@ -607,7 +608,7 @@
     <t>起きている相手をイタズラの対象にできる</t>
   </si>
   <si>
-    <t>mc_aun_ActWindMartialMultiHit</t>
+    <t>ActMCAUNWindMartialMultiHit</t>
   </si>
   <si>
     <t>一陣乱舞</t>
@@ -649,7 +650,7 @@
     <t>395820004</t>
   </si>
   <si>
-    <t>mc_aun_ActWindMartialSwarm</t>
+    <t>ActMCAUNWindMartialSwarm</t>
   </si>
   <si>
     <t>辻風払い</t>
@@ -673,13 +674,13 @@
     <t>395820005</t>
   </si>
   <si>
-    <t>mc_aun_ActWindMartialCounter</t>
+    <t>ActMCAUNWindMartialCounter</t>
   </si>
   <si>
     <t>凪返し</t>
   </si>
   <si>
-    <t>7</t>
+    <t>15</t>
   </si>
   <si>
     <t>Self</t>
@@ -688,7 +689,124 @@
     <t>ActMCAUNMartialCounter</t>
   </si>
   <si>
-    <t>次の行動まで構えを取り、攻撃してきた対象に強烈な反撃を行う。</t>
+    <t>neg,recovery</t>
+  </si>
+  <si>
+    <t>精神を研ぎ澄ませ、近鉄攻撃に対する回避と反撃の能力を得る。</t>
+  </si>
+  <si>
+    <t>curse</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>durationMax</t>
+  </si>
+  <si>
+    <t>hexPower</t>
+  </si>
+  <si>
+    <t>negate</t>
+  </si>
+  <si>
+    <t>defenseAttb</t>
+  </si>
+  <si>
+    <t>resistance</t>
+  </si>
+  <si>
+    <t>gainRes</t>
+  </si>
+  <si>
+    <t>nullify</t>
+  </si>
+  <si>
+    <t>phase</t>
+  </si>
+  <si>
+    <t>colors</t>
+  </si>
+  <si>
+    <t>element</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>strPhase_JP</t>
+  </si>
+  <si>
+    <t>strPhase</t>
+  </si>
+  <si>
+    <t>textEnd_JP</t>
+  </si>
+  <si>
+    <t>textEnd</t>
+  </si>
+  <si>
+    <t>textPhase2_JP</t>
+  </si>
+  <si>
+    <t>textPhase2</t>
+  </si>
+  <si>
+    <t>gradient</t>
+  </si>
+  <si>
+    <t>invert</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>p/10</t>
+  </si>
+  <si>
+    <t>0,1,2,3,4,5,6,7,8,9</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>ConMCAUNMartialCounter</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>counter,1,evasionPerfect,50</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
+    <t>martial</t>
+  </si>
+  <si>
+    <t>#1は精神を集中させ始めた。</t>
+  </si>
+  <si>
+    <t>#1 take(s) a counter stance.</t>
+  </si>
+  <si>
+    <t>#1は精神の集中を解いた。</t>
+  </si>
+  <si>
+    <t>#1 leave(s) the counter stance.</t>
+  </si>
+  <si>
+    <t>近接攻撃を高確率で回避し、反撃を行う構え。</t>
   </si>
 </sst>
 </file>
@@ -6466,7 +6584,7 @@
       <c r="BX3" s="4"/>
       <c r="BY3" s="4"/>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>176</v>
       </c>
@@ -6510,7 +6628,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>187</v>
       </c>
@@ -6554,7 +6672,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>395820003</v>
       </c>
@@ -6620,7 +6738,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>205</v>
       </c>
@@ -6682,7 +6800,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -6732,13 +6850,10 @@
         <v>200</v>
       </c>
       <c r="AB8" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="AR8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AV8" t="s">
         <v>212</v>
@@ -7728,4 +7843,297 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG4"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J1" t="s">
+        <v>224</v>
+      </c>
+      <c r="K1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N1" t="s">
+        <v>228</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" t="s">
+        <v>230</v>
+      </c>
+      <c r="S1" t="s">
+        <v>231</v>
+      </c>
+      <c r="T1" t="s">
+        <v>232</v>
+      </c>
+      <c r="U1" t="s">
+        <v>233</v>
+      </c>
+      <c r="V1" t="s">
+        <v>234</v>
+      </c>
+      <c r="W1" t="s">
+        <v>235</v>
+      </c>
+      <c r="X1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" t="s">
+        <v>57</v>
+      </c>
+      <c r="V2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" t="s">
+        <v>175</v>
+      </c>
+      <c r="R3" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O4" t="s">
+        <v>250</v>
+      </c>
+      <c r="R4" t="s">
+        <v>251</v>
+      </c>
+      <c r="S4" t="s">
+        <v>252</v>
+      </c>
+      <c r="T4" t="s">
+        <v>253</v>
+      </c>
+      <c r="U4" t="s">
+        <v>252</v>
+      </c>
+      <c r="V4" t="s">
+        <v>215</v>
+      </c>
+      <c r="X4" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>257</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="256">
   <si>
     <t>id</t>
   </si>
@@ -779,9 +779,6 @@
     <t>Buff</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>counter,1,evasionPerfect,50</t>
   </si>
   <si>
@@ -791,22 +788,16 @@
     <t>buff</t>
   </si>
   <si>
-    <t>martial</t>
+    <t>AI_Meditate</t>
   </si>
   <si>
     <t>#1は精神を集中させ始めた。</t>
   </si>
   <si>
-    <t>#1 take(s) a counter stance.</t>
-  </si>
-  <si>
     <t>#1は精神の集中を解いた。</t>
   </si>
   <si>
-    <t>#1 leave(s) the counter stance.</t>
-  </si>
-  <si>
-    <t>近接攻撃を高確率で回避し、反撃を行う構え。</t>
+    <t>近接攻撃に対する回避と反撃の能力を向上させる加護。</t>
   </si>
 </sst>
 </file>
@@ -8092,46 +8083,37 @@
         <v>248</v>
       </c>
       <c r="H4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O4" t="s">
         <v>249</v>
       </c>
-      <c r="I4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>250</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>251</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>252</v>
       </c>
-      <c r="T4" t="s">
-        <v>253</v>
-      </c>
       <c r="U4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V4" t="s">
         <v>215</v>
       </c>
       <c r="X4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z4" t="s">
         <v>254</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>257</v>
       </c>
       <c r="AE4" t="s">
         <v>63</v>
       </c>
       <c r="AF4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="259">
   <si>
     <t>id</t>
   </si>
@@ -311,7 +311,7 @@
     <t>1,100</t>
   </si>
   <si>
-    <t>ActMCAUNWindMartialSwarm/35,ActMCAUNWindMartialMultiHit/50,ActMCAUNWindMartialCounter/15</t>
+    <t>ActMCAUNWindMartialSwarm/35,ActMCAUNWindMartialMultiHit/50,ActMCAUNWindMartialCounter/20</t>
   </si>
   <si>
     <t>SPD/40,evasionPerfect/5,mod_flurry/30,mc_araj_featMonk/1</t>
@@ -686,9 +686,18 @@
     <t>Self</t>
   </si>
   <si>
+    <t>Buff,ConMCAUNMartialCounter</t>
+  </si>
+  <si>
     <t>ActMCAUNMartialCounter</t>
   </si>
   <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
     <t>neg,recovery</t>
   </si>
   <si>
@@ -779,13 +788,13 @@
     <t>Buff</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>counter,1,evasionPerfect,50</t>
   </si>
   <si>
     <t>0,0,0,0,0,0,0,0,0,0</t>
-  </si>
-  <si>
-    <t>buff</t>
   </si>
   <si>
     <t>AI_Meditate</t>
@@ -6810,12 +6819,6 @@
       <c r="K8" t="s">
         <v>64</v>
       </c>
-      <c r="O8" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" t="s">
-        <v>172</v>
-      </c>
       <c r="R8" t="s">
         <v>216</v>
       </c>
@@ -6825,8 +6828,11 @@
       <c r="U8" t="s">
         <v>217</v>
       </c>
+      <c r="V8" t="s">
+        <v>218</v>
+      </c>
       <c r="W8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X8" t="s">
         <v>198</v>
@@ -6835,16 +6841,19 @@
         <v>199</v>
       </c>
       <c r="Z8" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="AA8" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="AB8" t="s">
-        <v>219</v>
+        <v>222</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>210</v>
       </c>
       <c r="AR8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AV8" t="s">
         <v>212</v>
@@ -7861,55 +7870,55 @@
         <v>141</v>
       </c>
       <c r="G1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O1" t="s">
         <v>36</v>
       </c>
       <c r="P1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q1" t="s">
         <v>27</v>
       </c>
       <c r="R1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="S1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="U1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="V1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="W1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="X1" t="s">
         <v>159</v>
@@ -7918,22 +7927,22 @@
         <v>160</v>
       </c>
       <c r="Z1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AA1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AB1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AC1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AD1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AE1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AF1" t="s">
         <v>53</v>
@@ -8034,7 +8043,7 @@
         <v>55</v>
       </c>
       <c r="AE2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AF2" t="s">
         <v>55</v>
@@ -8048,10 +8057,10 @@
         <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I3" t="s">
         <v>61</v>
@@ -8060,10 +8069,10 @@
         <v>175</v>
       </c>
       <c r="R3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AD3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -8071,49 +8080,49 @@
         <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H4" t="s">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="O4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="R4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="S4" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="T4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U4" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="V4" t="s">
         <v>215</v>
       </c>
       <c r="X4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AE4" t="s">
         <v>63</v>
       </c>
       <c r="AF4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/SourceSheet.xlsx
@@ -245,7 +245,7 @@
     <t>Friend</t>
   </si>
   <si>
-    <t>addZone(tinkerCamp),addBio(),addDrama()</t>
+    <t>addBio(),addDrama()</t>
   </si>
   <si>
     <t>UniqueChara</t>
@@ -299,7 +299,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>addZone(palmia),addDrama(),addBio()</t>
+    <t>addDrama(),addBio()</t>
   </si>
   <si>
     <t>elea</t>
@@ -3693,7 +3693,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>213</v>
       </c>
